--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/arbeitsschutz/Betriebsklar-Nachpruefliste-Sifa.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/arbeitsschutz/Betriebsklar-Nachpruefliste-Sifa.xlsx
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: Inhalt seit Ihrer Freigabe geändert und/oder ohne unterschriebenes Blatt. Die Prüfsumme bestimmt die Fassung; jede Änderung ergibt eine neue.</t>
+          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu den Vorlagen liegen die aktuellen PDFs bei.</t>
+          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ffc268f69c4f</t>
+          <t>57c388f4fc2e</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 7893bbb50cc9 (bisherige Rechnung 73c536207bb5), heute ffc268f69c4f. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Die Vorlage enthält 3 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Die Vorlage enthält 3 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1e55038167de</t>
+          <t>c41d2dfd49b4</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung d586681a83ce (bisherige Rechnung e1f81534e968), heute 1e55038167de. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>9778504675c3</t>
+          <t>5c56ef6f4004</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 8c0f63e6bfad (bisherige Rechnung f041a0b04284), heute 9778504675c3. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>38cf09435e05</t>
+          <t>fc087228e53a</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 1115b5131c2e (bisherige Rechnung 599f83aa6405), heute 38cf09435e05. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „ohne die elektrotechnischen Grenzwerte“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „ohne die elektrotechnischen Grenzwerte“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>64202d9593ee</t>
+          <t>125ecb14e239</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung d4b49e166119 (bisherige Rechnung f477c1d03df5), heute 64202d9593ee. Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>231c565f2da1</t>
+          <t>2d674875e004</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung eb59ca0a4ae9 (bisherige Rechnung 32867a852a99), heute 231c565f2da1. Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>ae3880fbc6b7</t>
+          <t>c912c9a88d21</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung ff21254c0b11 (bisherige Rechnung ea45c72ec6fc), heute ae3880fbc6b7. Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Die Vorlage enthält 1 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Die Vorlage enthält 1 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>b4c705fdc2ed</t>
+          <t>757c3dfb104a</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 3c6d3887dc88 (bisherige Rechnung 1063d59082d4), heute b4c705fdc2ed. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 nennt einen unterschriebenen Nachtrag (Scan); er liegt uns nicht vor). Die Vorlage enthält 19 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 nennt einen unterschriebenen Nachtrag (Scan); er liegt uns nicht vor). Die Vorlage enthält 19 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5fea5ebbd667</t>
+          <t>339064dff284</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 4a810a9df8df (bisherige Rechnung 70fe591f5a3e), heute 5fea5ebbd667. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 nennt einen unterschriebenen Nachtrag (Scan); er liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 nennt einen unterschriebenen Nachtrag (Scan); er liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>

--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/arbeitsschutz/Betriebsklar-Nachpruefliste-Sifa.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/arbeitsschutz/Betriebsklar-Nachpruefliste-Sifa.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="So geht's" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nachprüfliste" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unterschrift" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,9 +33,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,10 +83,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,14 +467,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bitte prüfen und bestätigen. Diese Liste nennt alles, was nach unserer Durchsicht der Freigaben noch Ihre Prüfung oder Ihre Unterschrift braucht:</t>
+          <t>Bitte prüfen Sie die Positionen und bestätigen Sie sie per E-Mail. Diese Liste nennt alles, was nach unserer Durchsicht der Freigaben noch Ihre Prüfung oder Bestätigung braucht:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>• Unterschrift fehlt: Sie haben die Fassung freigegeben, uns liegt aber kein unterschriebenes Blatt vor. Bis dahin zeigt die App bei diesen Einträgen keinen Prüfvermerk.</t>
+          <t>• Bestätigung fehlt: Sie haben die Fassung freigegeben, uns liegt aber keine schriftliche Bestätigung vor. Bis dahin zeigt die App bei diesen Einträgen keinen Prüfvermerk.</t>
         </is>
       </c>
     </row>
@@ -496,7 +488,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
+          <t>• Vorlage: ohne schriftliche Bestätigung und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +512,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
+          <t>Bestätigen Sie bitte per E-Mail – eine Unterschrift ist nicht nötig. Es genügt eine kurze Antwort mit den Nummern der bestätigten Positionen, oder Sie schicken diese Datei mit ausgefüllter Spalte „Entscheidung“ mit Ihrer Antwort zurück. Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -535,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -616,7 +608,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Der Vermerk nennt jetzt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte bestätigen, dass die Einschränkung so richtig wiedergegeben ist.</t>
+          <t>Der Vermerk nennt jetzt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte bestätigen Sie per E-Mail, dass die Einschränkung so richtig wiedergegeben ist.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -628,27 +620,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Unterschrift fehlt</t>
+          <t>Einschränkung</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>E.54 arbeitsschutz.dguv_v3</t>
+          <t>E.53 arbeitsschutz.laerm</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Elektrische Geräte prüfen lassen</t>
+          <t>Lärm: messen, Gehörschutz und Lärmbereiche</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-23-nachpruefung-arbeitsschutz.xlsx, Stand 23.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt einen unterschriebenen Nachtrag als Scan; er liegt uns nicht vor). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
+          <t>Der Vermerk nennt jetzt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte bestätigen Sie per E-Mail, dass die Einschränkung so richtig wiedergegeben ist.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -660,27 +652,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Unterschrift fehlt</t>
+          <t>Vorlage</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>E.54 arbeitsschutz.flucht_rettungsplan</t>
+          <t>unterweisung</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>57c388f4fc2e</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Flucht- und Rettungsplan prüfen</t>
+          <t>Unterweisungsnachweis</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-25-arbeitsschutz-mail.txt, Stand 25.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 (2026-10-25-arbeitsschutz-mail.txt) nennt den unterschriebenen zweiten Nachtrag als Scan; er liegt uns nicht vor). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
+          <t>Die Vorlage enthält 3 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor. Bitte prüfen Sie die mit „fachlich zu prüfen“ gekennzeichneten Stellen und bestätigen Sie sie per E-Mail bzw. nennen Sie die Änderung.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -692,27 +684,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Einschränkung</t>
+          <t>Vorlage</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>E.53 arbeitsschutz.laerm</t>
+          <t>pruefprotokoll_elektro</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>fc087228e53a</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Lärm: messen, Gehörschutz und Lärmbereiche</t>
+          <t>Prüfprotokoll elektrische Geräte (DGUV V3)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Der Vermerk nennt jetzt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Bitte bestätigen, dass die Einschränkung so richtig wiedergegeben ist.</t>
+          <t>Der Vermerk nennt Ihre Einschränkung: „ohne die elektrotechnischen Grenzwerte“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor; bitte bestätigen Sie per E-Mail nur, dass der Vermerk so richtig ist.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -724,27 +716,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Unterschrift fehlt</t>
+          <t>Vorlage</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>H.1 branche.gastro_schankanlage_fluessiggas</t>
+          <t>betriebsanweisung</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>125ecb14e239</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Getränkeschankanlage und Flüssiggasanlage prüfen lassen</t>
+          <t>Betriebsanweisung</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-25-arbeitsschutz-mail.txt, Stand 25.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 (2026-10-25-arbeitsschutz-mail.txt) nennt den unterschriebenen zweiten Nachtrag als Scan; er liegt uns nicht vor). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
+          <t>Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor; bitte bestätigen Sie per E-Mail nur, dass der Vermerk so richtig ist.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -761,22 +753,22 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>unterweisung</t>
+          <t>expositionsverzeichnis</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57c388f4fc2e</t>
+          <t>2d674875e004</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Unterweisungsnachweis</t>
+          <t>Expositionsverzeichnis</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Die Vorlage enthält 3 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
+          <t>Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor; bitte bestätigen Sie per E-Mail nur, dass der Vermerk so richtig ist.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -793,22 +785,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>gefahrstoffverzeichnis</t>
+          <t>hautschutzplan</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>c41d2dfd49b4</t>
+          <t>c912c9a88d21</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Gefahrstoffverzeichnis</t>
+          <t>Hautschutzplan</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
+          <t>Die Vorlage enthält 1 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor. Bitte prüfen Sie die mit „fachlich zu prüfen“ gekennzeichneten Stellen und bestätigen Sie sie per E-Mail bzw. nennen Sie die Änderung.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -825,22 +817,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>betriebsanweisung_maschine</t>
+          <t>gefaehrdungsbeurteilung</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5c56ef6f4004</t>
+          <t>757c3dfb104a</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Betriebsanweisung Maschinen</t>
+          <t>Gefährdungsbeurteilung</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
+          <t>Die Vorlage enthält 19 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor. Bitte prüfen Sie die mit „fachlich zu prüfen“ gekennzeichneten Stellen und bestätigen Sie sie per E-Mail bzw. nennen Sie die Änderung.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -857,22 +849,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>pruefprotokoll_elektro</t>
+          <t>betriebsanweisung_biostoffe</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>fc087228e53a</t>
+          <t>339064dff284</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Prüfprotokoll elektrische Geräte (DGUV V3)</t>
+          <t>Betriebsanweisung Biostoffe</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-arbeitsschutz-mail.txt) nennt ein unterschriebenes Bestätigungsblatt (Scan); es liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „ohne die elektrotechnischen Grenzwerte“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
+          <t>Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Ihre Freigabe dieser Fassung liegt uns schriftlich vor; bitte bestätigen Sie per E-Mail nur, dass der Vermerk so richtig ist.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -884,291 +876,39 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Vorlage</t>
+          <t>Nennung im Vermerk</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>betriebsanweisung</t>
+          <t>alle</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>125ecb14e239</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Betriebsanweisung</t>
+          <t>Rolle statt Name</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
+          <t>Die App nennt Personen nicht mehr. Bisher ohne Namen: „Inhalt fachlich geprüft, Stand …“ (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Inhalt fachlich geprüft von einer Fachkraft für Arbeitssicherheit, Stand …. Die Prüfung betrifft die allgemeinen Inhalte, nicht deinen Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen Sie per E-Mail, dass die Nennung der Rolle so in Ordnung ist.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>expositionsverzeichnis</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2d674875e004</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Expositionsverzeichnis</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>hautschutzplan</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>c912c9a88d21</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Hautschutzplan</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Das Blatt (2026-10-23-bestaetigung-vorlagen-arbeitsschutz-runde3.pdf) trägt keine Unterschrift). Die Vorlage enthält 1 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>gefaehrdungsbeurteilung</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>757c3dfb104a</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Gefährdungsbeurteilung</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 nennt einen unterschriebenen Nachtrag (Scan); er liegt uns nicht vor). Die Vorlage enthält 19 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>betriebsanweisung_biostoffe</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>339064dff284</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Betriebsanweisung Biostoffe</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 nennt einen unterschriebenen Nachtrag (Scan); er liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „ohne arbeitsmedizinische Angaben“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Nennung im Vermerk</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>alle</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Rolle statt Name</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Die App nennt Personen nicht mehr. Bisher ohne Namen: „Inhalt fachlich geprüft, Stand …“ (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Inhalt fachlich geprüft von einer Fachkraft für Arbeitssicherheit, Stand …. Die Prüfung betrifft die allgemeinen Inhalte, nicht deinen Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen, dass die Nennung der Rolle so in Ordnung ist.</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,ändern (Anmerkung),nicht mein Bereich"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bestätigung der Nachprüfung – Fachkraft für Arbeitssicherheit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Ich habe die Positionen der Nachprüfliste vom 25.10.2026, die ich in der Spalte „Entscheidung“ mit „bestätigt“ markiert habe, in der jeweils genannten Fassung (Version bzw. Prüfsumme) fachlich geprüft bzw. durchgesehen. Sie sind nach meiner Prüfung zum genannten Stand zutreffend. Positionen mit „ändern“ oder „nicht mein Bereich“ sind nicht umfasst; für sie darf kein Vermerk angezeigt werden. Ändert sich ein Eintrag (neue Version) oder eine Vorlage (andere Prüfsumme), gilt diese Bestätigung dafür nicht mehr. Die Prüfung betrifft die allgemeinen Inhalte, nicht ihre Anwendung im Einzelfall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Anzeige in der App (nur bei bestätigten Positionen, ohne Namen, mit der Rolle): „Inhalt fachlich geprüft von einer Fachkraft für Arbeitssicherheit, Stand …. Die Prüfung betrifft die allgemeinen Inhalte, nicht deinen Einzelfall.“</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Stand der Prüfung:</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Ort, Datum:</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Unterschrift:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>(Fachkraft für Arbeitssicherheit)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:B5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>